--- a/data/trans_camb/IP1016-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1016-Edad-trans_camb.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
     </row>
